--- a/virtual-physics-lab/app/dl/ASRJC_Q1_wire_circuit.xlsx
+++ b/virtual-physics-lab/app/dl/ASRJC_Q1_wire_circuit.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,10 +101,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -671,64 +672,64 @@
       <c r="A6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>2.18</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>1.94</v>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>1.89</v>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>1.86</v>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>1.83</v>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -802,14 +803,14 @@
       <c r="A6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>2.18</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>(3.04-B6)/(A6/100)</f>
         <v/>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>P = gradient</t>
         </is>
@@ -818,7 +819,7 @@
         <f>SLOPE(C6:C12,B6:B12)</f>
         <v/>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>m⁻¹</t>
         </is>
@@ -828,14 +829,14 @@
       <c r="A7" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>2.08</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>(3.04-B7)/(A7/100)</f>
         <v/>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Q = −intercept</t>
         </is>
@@ -844,7 +845,7 @@
         <f>-INTERCEPT(C6:C12,B6:B12)</f>
         <v/>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>V m⁻¹</t>
         </is>
@@ -854,14 +855,14 @@
       <c r="A8" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>(3.04-B8)/(A8/100)</f>
         <v/>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Q/P (expect E/2)</t>
         </is>
@@ -870,7 +871,7 @@
         <f>-INTERCEPT(C6:C12,B6:B12)/SLOPE(C6:C12,B6:B12)</f>
         <v/>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -880,10 +881,10 @@
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>1.94</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>(3.04-B9)/(A9/100)</f>
         <v/>
       </c>
@@ -892,10 +893,10 @@
       <c r="A10" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>1.89</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>(3.04-B10)/(A10/100)</f>
         <v/>
       </c>
@@ -904,10 +905,10 @@
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>1.86</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>(3.04-B11)/(A11/100)</f>
         <v/>
       </c>
@@ -916,10 +917,10 @@
       <c r="A12" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>1.83</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>(3.04-B12)/(A12/100)</f>
         <v/>
       </c>
